--- a/2022 data/excel_outputs/328_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/328_boothwise_data.xlsx
@@ -14,11 +14,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="544">
   <si>
     <t>AC 328 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -436,7 +499,7 @@
     <t>PRIMARY SCHOOL NAGWA PREM</t>
   </si>
   <si>
-    <t>PRIMARY SCHOOL CHAK■ SARAYA</t>
+    <t>SHRCH0 DY0 J0 JBHPDAJ|DAMCH JBH|DAT CH CHABH BBHCH|J JBH</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL BATH BUJURG PURAV</t>
@@ -1589,8 +1652,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1606,7 +1677,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1614,12 +1685,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1918,76 +2007,139 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="D2" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="E2" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="F2" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="G2" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="H2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="I2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="J2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="K2" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="L2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="M2" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="N2" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="O2" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="P2" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="Q2" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="R2" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="S2" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="T2" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="U2" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="V2" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1995,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>926</v>
@@ -2063,7 +2215,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>974</v>
@@ -2131,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>1059</v>
@@ -2199,7 +2351,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>699</v>
@@ -2267,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>791</v>
@@ -2335,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>556</v>
@@ -2403,7 +2555,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>955</v>
@@ -2471,7 +2623,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1055</v>
@@ -2539,7 +2691,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>641</v>
@@ -2607,7 +2759,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>807</v>
@@ -2675,7 +2827,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>709</v>
@@ -2743,7 +2895,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>711</v>
@@ -2811,7 +2963,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>913</v>
@@ -2879,7 +3031,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>1142</v>
@@ -2947,7 +3099,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>1109</v>
@@ -3015,7 +3167,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>938</v>
@@ -3083,7 +3235,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>886</v>
@@ -3151,7 +3303,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>632</v>
@@ -3219,7 +3371,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>612</v>
@@ -3287,7 +3439,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>1072</v>
@@ -3355,7 +3507,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>598</v>
@@ -3423,7 +3575,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>783</v>
@@ -3491,7 +3643,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>821</v>
@@ -3559,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>809</v>
@@ -3627,7 +3779,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>756</v>
@@ -3695,7 +3847,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1106</v>
@@ -3763,7 +3915,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>673</v>
@@ -3831,7 +3983,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>618</v>
@@ -3899,7 +4051,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>461</v>
@@ -3967,7 +4119,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1149</v>
@@ -4035,7 +4187,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1028</v>
@@ -4103,7 +4255,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1119</v>
@@ -4171,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>789</v>
@@ -4239,7 +4391,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>907</v>
@@ -4307,7 +4459,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>789</v>
@@ -4375,7 +4527,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>908</v>
@@ -4443,7 +4595,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>829</v>
@@ -4511,7 +4663,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>485</v>
@@ -4579,7 +4731,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>730</v>
@@ -4647,7 +4799,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>670</v>
@@ -4715,7 +4867,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C43">
         <v>999</v>
@@ -4783,7 +4935,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>1082</v>
@@ -4851,7 +5003,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C45">
         <v>1217</v>
@@ -4919,7 +5071,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>832</v>
@@ -4987,7 +5139,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>954</v>
@@ -5055,7 +5207,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>1073</v>
@@ -5123,7 +5275,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>659</v>
@@ -5191,7 +5343,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>681</v>
@@ -5259,7 +5411,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>687</v>
@@ -5327,7 +5479,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>735</v>
@@ -5395,7 +5547,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>1006</v>
@@ -5463,7 +5615,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>782</v>
@@ -5531,7 +5683,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>493</v>
@@ -5599,7 +5751,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>1125</v>
@@ -5667,7 +5819,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>975</v>
@@ -5735,7 +5887,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>1039</v>
@@ -5803,7 +5955,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>937</v>
@@ -5871,7 +6023,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>1138</v>
@@ -5939,7 +6091,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>652</v>
@@ -6007,7 +6159,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>1127</v>
@@ -6075,7 +6227,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>702</v>
@@ -6143,7 +6295,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>516</v>
@@ -6211,7 +6363,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>750</v>
@@ -6279,7 +6431,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>1095</v>
@@ -6347,7 +6499,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>763</v>
@@ -6415,7 +6567,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>879</v>
@@ -6483,7 +6635,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>839</v>
@@ -6551,7 +6703,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>737</v>
@@ -6619,7 +6771,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>1024</v>
@@ -6687,7 +6839,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>439</v>
@@ -6755,7 +6907,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C73">
         <v>421</v>
@@ -6823,7 +6975,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C74">
         <v>721</v>
@@ -6891,7 +7043,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>908</v>
@@ -6959,7 +7111,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>980</v>
@@ -7027,7 +7179,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>1072</v>
@@ -7095,7 +7247,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>990</v>
@@ -7163,7 +7315,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>1066</v>
@@ -7231,7 +7383,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>1062</v>
@@ -7299,7 +7451,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>1041</v>
@@ -7367,7 +7519,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>685</v>
@@ -7435,7 +7587,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>627</v>
@@ -7503,7 +7655,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>670</v>
@@ -7571,7 +7723,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>595</v>
@@ -7639,7 +7791,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>787</v>
@@ -7707,7 +7859,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>1099</v>
@@ -7775,7 +7927,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>929</v>
@@ -7843,7 +7995,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>541</v>
@@ -7911,7 +8063,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>893</v>
@@ -7979,7 +8131,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>863</v>
@@ -8047,7 +8199,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>640</v>
@@ -8115,7 +8267,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>800</v>
@@ -8183,7 +8335,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>1002</v>
@@ -8251,7 +8403,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>728</v>
@@ -8319,7 +8471,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>499</v>
@@ -8387,7 +8539,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>640</v>
@@ -8455,7 +8607,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>626</v>
@@ -8523,7 +8675,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>1148</v>
@@ -8591,7 +8743,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>870</v>
@@ -8659,7 +8811,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>581</v>
@@ -8727,7 +8879,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>1014</v>
@@ -8795,7 +8947,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>674</v>
@@ -8863,7 +9015,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>860</v>
@@ -8931,7 +9083,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>1049</v>
@@ -8999,7 +9151,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>677</v>
@@ -9067,7 +9219,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>1056</v>
@@ -9135,7 +9287,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>724</v>
@@ -9203,7 +9355,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>909</v>
@@ -9271,7 +9423,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C110">
         <v>499</v>
@@ -9339,7 +9491,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C111">
         <v>1047</v>
@@ -9407,7 +9559,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C112">
         <v>627</v>
@@ -9475,7 +9627,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C113">
         <v>937</v>
@@ -9543,7 +9695,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C114">
         <v>982</v>
@@ -9611,7 +9763,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C115">
         <v>634</v>
@@ -9679,7 +9831,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C116">
         <v>649</v>
@@ -9747,7 +9899,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C117">
         <v>755</v>
@@ -9815,7 +9967,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C118">
         <v>657</v>
@@ -9883,7 +10035,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C119">
         <v>981</v>
@@ -9951,7 +10103,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C120">
         <v>828</v>
@@ -10019,7 +10171,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C121">
         <v>619</v>
@@ -10087,7 +10239,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C122">
         <v>637</v>
@@ -10155,7 +10307,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C123">
         <v>765</v>
@@ -10223,7 +10375,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C124">
         <v>566</v>
@@ -10291,7 +10443,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C125">
         <v>705</v>
@@ -10359,7 +10511,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C126">
         <v>617</v>
@@ -10427,7 +10579,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C127">
         <v>522</v>
@@ -10495,7 +10647,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C128">
         <v>666</v>
@@ -10563,7 +10715,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C129">
         <v>988</v>
@@ -10631,7 +10783,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C130">
         <v>1185</v>
@@ -10699,7 +10851,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C131">
         <v>1013</v>
@@ -10767,7 +10919,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C132">
         <v>811</v>
@@ -10835,7 +10987,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C133">
         <v>975</v>
@@ -10903,7 +11055,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C134">
         <v>1055</v>
@@ -10971,7 +11123,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C135">
         <v>674</v>
@@ -11039,7 +11191,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C136">
         <v>826</v>
@@ -11107,7 +11259,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C137">
         <v>864</v>
@@ -11175,7 +11327,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C138">
         <v>839</v>
@@ -11243,7 +11395,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C139">
         <v>1155</v>
@@ -11311,7 +11463,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C140">
         <v>1003</v>
@@ -11379,7 +11531,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C141">
         <v>962</v>
@@ -11447,7 +11599,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C142">
         <v>1006</v>
@@ -11515,7 +11667,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C143">
         <v>711</v>
@@ -11583,7 +11735,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C144">
         <v>683</v>
@@ -11651,7 +11803,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C145">
         <v>661</v>
@@ -11719,7 +11871,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C146">
         <v>666</v>
@@ -11787,7 +11939,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C147">
         <v>632</v>
@@ -11855,7 +12007,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C148">
         <v>430</v>
@@ -11923,7 +12075,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C149">
         <v>1021</v>
@@ -11991,7 +12143,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C150">
         <v>735</v>
@@ -12059,7 +12211,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C151">
         <v>1086</v>
@@ -12127,7 +12279,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C152">
         <v>797</v>
@@ -12195,7 +12347,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C153">
         <v>735</v>
@@ -12263,7 +12415,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C154">
         <v>467</v>
@@ -12331,7 +12483,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C155">
         <v>794</v>
@@ -12399,7 +12551,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C156">
         <v>873</v>
@@ -12467,7 +12619,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C157">
         <v>585</v>
@@ -12535,7 +12687,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C158">
         <v>891</v>
@@ -12603,7 +12755,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C159">
         <v>846</v>
@@ -12671,7 +12823,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C160">
         <v>650</v>
@@ -12739,7 +12891,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C161">
         <v>1050</v>
@@ -12807,7 +12959,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C162">
         <v>696</v>
@@ -12875,7 +13027,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C163">
         <v>1163</v>
@@ -12943,7 +13095,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C164">
         <v>718</v>
@@ -13011,7 +13163,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C165">
         <v>878</v>
@@ -13079,7 +13231,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C166">
         <v>836</v>
@@ -13147,7 +13299,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C167">
         <v>681</v>
@@ -13215,7 +13367,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C168">
         <v>770</v>
@@ -13283,7 +13435,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C169">
         <v>833</v>
@@ -13351,7 +13503,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C170">
         <v>876</v>
@@ -13419,7 +13571,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C171">
         <v>711</v>
@@ -13487,7 +13639,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C172">
         <v>1093</v>
@@ -13555,7 +13707,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C173">
         <v>701</v>
@@ -13623,7 +13775,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C174">
         <v>475</v>
@@ -13691,7 +13843,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C175">
         <v>1000</v>
@@ -13759,7 +13911,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C176">
         <v>358</v>
@@ -13827,7 +13979,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C177">
         <v>1136</v>
@@ -13895,7 +14047,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C178">
         <v>930</v>
@@ -13963,7 +14115,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C179">
         <v>762</v>
@@ -14031,7 +14183,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C180">
         <v>1076</v>
@@ -14099,7 +14251,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C181">
         <v>773</v>
@@ -14167,7 +14319,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C182">
         <v>957</v>
@@ -14235,7 +14387,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C183">
         <v>1158</v>
@@ -14303,7 +14455,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C184">
         <v>1003</v>
@@ -14371,7 +14523,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C185">
         <v>821</v>
@@ -14439,7 +14591,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C186">
         <v>823</v>
@@ -14507,7 +14659,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C187">
         <v>875</v>
@@ -14575,7 +14727,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C188">
         <v>851</v>
@@ -14643,7 +14795,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C189">
         <v>1103</v>
@@ -14711,7 +14863,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C190">
         <v>1206</v>
@@ -14779,7 +14931,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C191">
         <v>861</v>
@@ -14847,7 +14999,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>653</v>
@@ -14915,7 +15067,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>907</v>
@@ -14983,7 +15135,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>863</v>
@@ -15051,7 +15203,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>793</v>
@@ -15119,7 +15271,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>920</v>
@@ -15187,7 +15339,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>661</v>
@@ -15255,7 +15407,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C198">
         <v>958</v>
@@ -15323,7 +15475,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C199">
         <v>1016</v>
@@ -15391,7 +15543,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C200">
         <v>408</v>
@@ -15459,7 +15611,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C201">
         <v>1119</v>
@@ -15527,7 +15679,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C202">
         <v>1099</v>
@@ -15595,7 +15747,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C203">
         <v>969</v>
@@ -15663,7 +15815,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C204">
         <v>971</v>
@@ -15731,7 +15883,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C205">
         <v>941</v>
@@ -15799,7 +15951,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C206">
         <v>950</v>
@@ -15867,7 +16019,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C207">
         <v>1064</v>
@@ -15935,7 +16087,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C208">
         <v>989</v>
@@ -16003,7 +16155,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C209">
         <v>1087</v>
@@ -16071,7 +16223,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C210">
         <v>912</v>
@@ -16139,7 +16291,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C211">
         <v>661</v>
@@ -16207,7 +16359,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C212">
         <v>1019</v>
@@ -16275,7 +16427,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C213">
         <v>718</v>
@@ -16343,7 +16495,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C214">
         <v>684</v>
@@ -16411,7 +16563,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C215">
         <v>1011</v>
@@ -16479,7 +16631,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C216">
         <v>710</v>
@@ -16547,7 +16699,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C217">
         <v>621</v>
@@ -16615,7 +16767,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="C218">
         <v>1045</v>
@@ -16683,7 +16835,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C219">
         <v>1056</v>
@@ -16751,7 +16903,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C220">
         <v>1061</v>
@@ -16819,7 +16971,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C221">
         <v>696</v>
@@ -16887,7 +17039,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C222">
         <v>648</v>
@@ -16955,7 +17107,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C223">
         <v>883</v>
@@ -17023,7 +17175,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C224">
         <v>635</v>
@@ -17091,7 +17243,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C225">
         <v>748</v>
@@ -17159,7 +17311,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="C226">
         <v>1148</v>
@@ -17227,7 +17379,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="C227">
         <v>1037</v>
@@ -17295,7 +17447,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C228">
         <v>894</v>
@@ -17363,7 +17515,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C229">
         <v>642</v>
@@ -17431,7 +17583,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C230">
         <v>787</v>
@@ -17499,7 +17651,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C231">
         <v>716</v>
@@ -17567,7 +17719,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="C232">
         <v>874</v>
@@ -17635,7 +17787,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="C233">
         <v>751</v>
@@ -17703,7 +17855,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C234">
         <v>618</v>
@@ -17771,7 +17923,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C235">
         <v>1028</v>
@@ -17839,7 +17991,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="C236">
         <v>991</v>
@@ -17907,7 +18059,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C237">
         <v>898</v>
@@ -17975,7 +18127,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C238">
         <v>916</v>
@@ -18043,7 +18195,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C239">
         <v>814</v>
@@ -18111,7 +18263,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C240">
         <v>559</v>
@@ -18179,7 +18331,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C241">
         <v>739</v>
@@ -18247,7 +18399,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C242">
         <v>614</v>
@@ -18315,7 +18467,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="C243">
         <v>1042</v>
@@ -18383,7 +18535,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C244">
         <v>967</v>
@@ -18451,7 +18603,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C245">
         <v>652</v>
@@ -18519,7 +18671,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C246">
         <v>941</v>
@@ -18587,7 +18739,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C247">
         <v>445</v>
@@ -18655,7 +18807,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C248">
         <v>1030</v>
@@ -18723,7 +18875,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C249">
         <v>1070</v>
@@ -18791,7 +18943,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C250">
         <v>1134</v>
@@ -18859,7 +19011,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C251">
         <v>1162</v>
@@ -18927,7 +19079,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C252">
         <v>1098</v>
@@ -18995,7 +19147,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C253">
         <v>956</v>
@@ -19063,7 +19215,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C254">
         <v>667</v>
@@ -19131,7 +19283,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C255">
         <v>790</v>
@@ -19199,7 +19351,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="C256">
         <v>683</v>
@@ -19267,7 +19419,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C257">
         <v>607</v>
@@ -19335,7 +19487,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="C258">
         <v>1159</v>
@@ -19403,7 +19555,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="C259">
         <v>875</v>
@@ -19471,7 +19623,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C260">
         <v>1171</v>
@@ -19539,7 +19691,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C261">
         <v>930</v>
@@ -19607,7 +19759,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C262">
         <v>937</v>
@@ -19675,7 +19827,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C263">
         <v>1082</v>
@@ -19743,7 +19895,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C264">
         <v>473</v>
@@ -19811,7 +19963,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C265">
         <v>870</v>
@@ -19879,7 +20031,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="C266">
         <v>750</v>
@@ -19947,7 +20099,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="C267">
         <v>817</v>
@@ -20015,7 +20167,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C268">
         <v>1133</v>
@@ -20083,7 +20235,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="C269">
         <v>504</v>
@@ -20151,7 +20303,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C270">
         <v>720</v>
@@ -20219,7 +20371,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="C271">
         <v>821</v>
@@ -20287,7 +20439,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C272">
         <v>1042</v>
@@ -20355,7 +20507,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C273">
         <v>797</v>
@@ -20423,7 +20575,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C274">
         <v>743</v>
@@ -20491,7 +20643,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C275">
         <v>630</v>
@@ -20559,7 +20711,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C276">
         <v>642</v>
@@ -20627,7 +20779,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C277">
         <v>644</v>
@@ -20695,7 +20847,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C278">
         <v>672</v>
@@ -20763,7 +20915,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C279">
         <v>975</v>
@@ -20831,7 +20983,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C280">
         <v>1062</v>
@@ -20899,7 +21051,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C281">
         <v>525</v>
@@ -20967,7 +21119,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C282">
         <v>751</v>
@@ -21035,7 +21187,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="C283">
         <v>827</v>
@@ -21103,7 +21255,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C284">
         <v>1007</v>
@@ -21171,7 +21323,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C285">
         <v>854</v>
@@ -21239,7 +21391,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="C286">
         <v>770</v>
@@ -21307,7 +21459,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C287">
         <v>495</v>
@@ -21375,7 +21527,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C288">
         <v>695</v>
@@ -21443,7 +21595,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C289">
         <v>877</v>
@@ -21511,7 +21663,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C290">
         <v>976</v>
@@ -21579,7 +21731,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C291">
         <v>1095</v>
@@ -21647,7 +21799,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C292">
         <v>1168</v>
@@ -21715,7 +21867,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C293">
         <v>1120</v>
@@ -21783,7 +21935,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C294">
         <v>1092</v>
@@ -21851,7 +22003,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C295">
         <v>667</v>
@@ -21919,7 +22071,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C296">
         <v>750</v>
@@ -21987,7 +22139,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C297">
         <v>925</v>
@@ -22055,7 +22207,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C298">
         <v>938</v>
@@ -22123,7 +22275,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C299">
         <v>700</v>
@@ -22191,7 +22343,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C300">
         <v>1045</v>
@@ -22259,7 +22411,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C301">
         <v>835</v>
@@ -22327,7 +22479,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C302">
         <v>735</v>
@@ -22395,7 +22547,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C303">
         <v>699</v>
@@ -22463,7 +22615,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C304">
         <v>909</v>
@@ -22531,7 +22683,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C305">
         <v>704</v>
@@ -22599,7 +22751,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C306">
         <v>762</v>
@@ -22667,7 +22819,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C307">
         <v>644</v>
@@ -22735,7 +22887,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C308">
         <v>968</v>
@@ -22803,7 +22955,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C309">
         <v>754</v>
@@ -22871,7 +23023,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C310">
         <v>479</v>
@@ -22939,7 +23091,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C311">
         <v>1086</v>
@@ -23007,7 +23159,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C312">
         <v>1018</v>
@@ -23075,7 +23227,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C313">
         <v>605</v>
@@ -23143,7 +23295,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C314">
         <v>781</v>
@@ -23211,7 +23363,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C315">
         <v>949</v>
@@ -23279,7 +23431,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C316">
         <v>826</v>
@@ -23347,7 +23499,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C317">
         <v>802</v>
@@ -23415,7 +23567,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C318">
         <v>588</v>
@@ -23483,7 +23635,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="C319">
         <v>745</v>
@@ -23551,7 +23703,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C320">
         <v>1130</v>
@@ -23619,7 +23771,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C321">
         <v>820</v>
@@ -23687,7 +23839,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C322">
         <v>689</v>
@@ -23755,7 +23907,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C323">
         <v>636</v>
@@ -23823,7 +23975,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C324">
         <v>1087</v>
@@ -23891,7 +24043,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C325">
         <v>788</v>
@@ -23959,7 +24111,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C326">
         <v>1134</v>
@@ -24027,7 +24179,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C327">
         <v>1061</v>
@@ -24095,7 +24247,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C328">
         <v>1010</v>
@@ -24163,7 +24315,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C329">
         <v>1031</v>
@@ -24231,7 +24383,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C330">
         <v>1137</v>
@@ -24299,7 +24451,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="C331">
         <v>625</v>
@@ -24367,7 +24519,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C332">
         <v>608</v>
@@ -24435,7 +24587,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C333">
         <v>885</v>
@@ -24503,7 +24655,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C334">
         <v>723</v>
@@ -24571,7 +24723,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C335">
         <v>1124</v>
@@ -24639,7 +24791,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="C336">
         <v>748</v>
@@ -24707,7 +24859,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C337">
         <v>531</v>
@@ -24775,7 +24927,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C338">
         <v>589</v>
@@ -24843,7 +24995,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C339">
         <v>623</v>
@@ -24911,7 +25063,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="C340">
         <v>612</v>
@@ -24979,7 +25131,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C341">
         <v>999</v>
@@ -25047,7 +25199,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="C342">
         <v>485</v>
@@ -25115,7 +25267,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C343">
         <v>1071</v>
@@ -25183,7 +25335,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C344">
         <v>1155</v>
@@ -25251,7 +25403,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="C345">
         <v>748</v>
@@ -25319,7 +25471,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="C346">
         <v>876</v>
@@ -25387,7 +25539,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C347">
         <v>587</v>
@@ -25455,7 +25607,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C348">
         <v>761</v>
@@ -25523,7 +25675,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C349">
         <v>480</v>
@@ -25591,7 +25743,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C350">
         <v>667</v>
@@ -25659,7 +25811,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C351">
         <v>999</v>
@@ -25727,7 +25879,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C352">
         <v>999</v>
@@ -25795,7 +25947,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="C353">
         <v>665</v>
@@ -25863,7 +26015,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C354">
         <v>604</v>
@@ -25931,7 +26083,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C355">
         <v>482</v>
@@ -25999,7 +26151,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="C356">
         <v>1147</v>
@@ -26067,7 +26219,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C357">
         <v>1118</v>
@@ -26135,7 +26287,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C358">
         <v>1116</v>
@@ -26203,7 +26355,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C359">
         <v>932</v>
@@ -26271,7 +26423,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C360">
         <v>891</v>
@@ -26339,7 +26491,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C361">
         <v>750</v>
@@ -26407,7 +26559,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C362">
         <v>1056</v>
@@ -26475,7 +26627,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C363">
         <v>957</v>
@@ -26543,7 +26695,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C364">
         <v>367</v>
@@ -26611,7 +26763,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C365">
         <v>925</v>
@@ -26679,7 +26831,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C366">
         <v>901</v>
@@ -26747,7 +26899,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C367">
         <v>982</v>
@@ -26815,7 +26967,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C368">
         <v>1020</v>
@@ -26883,7 +27035,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C369">
         <v>977</v>
@@ -26951,7 +27103,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C370">
         <v>877</v>
@@ -27019,7 +27171,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C371">
         <v>716</v>
@@ -27087,7 +27239,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C372">
         <v>949</v>
@@ -27155,7 +27307,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="C373">
         <v>899</v>
@@ -27223,7 +27375,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="C374">
         <v>657</v>
@@ -27291,7 +27443,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C375">
         <v>672</v>
@@ -27359,7 +27511,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C376">
         <v>626</v>
@@ -27427,7 +27579,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C377">
         <v>954</v>
@@ -27495,7 +27647,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C378">
         <v>870</v>
@@ -27563,7 +27715,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C379">
         <v>802</v>
@@ -27631,7 +27783,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="C380">
         <v>978</v>
@@ -27699,7 +27851,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C381">
         <v>1106</v>
@@ -27767,7 +27919,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C382">
         <v>1091</v>
@@ -27835,7 +27987,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C383">
         <v>1024</v>
@@ -27903,7 +28055,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C384">
         <v>1143</v>
@@ -27971,7 +28123,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="C385">
         <v>679</v>
@@ -28039,7 +28191,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="C386">
         <v>857</v>
@@ -28107,7 +28259,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C387">
         <v>1089</v>
@@ -28175,7 +28327,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C388">
         <v>965</v>
@@ -28243,7 +28395,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="C389">
         <v>636</v>
@@ -28311,7 +28463,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C390">
         <v>642</v>
@@ -28379,7 +28531,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="C391">
         <v>682</v>
@@ -28447,7 +28599,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="C392">
         <v>581</v>
@@ -28515,7 +28667,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C393">
         <v>874</v>
@@ -28583,7 +28735,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C394">
         <v>906</v>
@@ -28651,7 +28803,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C395">
         <v>1033</v>
@@ -28719,7 +28871,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C396">
         <v>696</v>
@@ -28787,7 +28939,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="C397">
         <v>639</v>
@@ -28855,7 +29007,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="C398">
         <v>1081</v>
@@ -28923,7 +29075,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C399">
         <v>1086</v>
@@ -28991,7 +29143,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="C400">
         <v>966</v>
@@ -29059,7 +29211,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C401">
         <v>710</v>
@@ -29127,7 +29279,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C402">
         <v>718</v>
@@ -29195,7 +29347,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C403">
         <v>1134</v>
@@ -29263,7 +29415,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="C404">
         <v>611</v>
@@ -29331,7 +29483,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C405">
         <v>787</v>
@@ -29399,7 +29551,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="C406">
         <v>641</v>
@@ -29467,7 +29619,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C407">
         <v>636</v>
@@ -29535,7 +29687,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="C408">
         <v>557</v>
@@ -29603,7 +29755,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="C409">
         <v>1127</v>
@@ -29671,7 +29823,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C410">
         <v>1065</v>
@@ -29739,7 +29891,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C411">
         <v>606</v>
@@ -29807,7 +29959,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C412">
         <v>751</v>
@@ -29875,7 +30027,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C413">
         <v>830</v>
@@ -29943,7 +30095,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="C414">
         <v>1138</v>
@@ -30011,7 +30163,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="C415">
         <v>1178</v>
@@ -30079,7 +30231,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="C416">
         <v>947</v>
@@ -30147,7 +30299,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C417">
         <v>983</v>
@@ -30215,7 +30367,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="C418">
         <v>732</v>
@@ -30283,7 +30435,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C419">
         <v>655</v>
@@ -30351,7 +30503,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="C420">
         <v>706</v>
@@ -30419,7 +30571,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C421">
         <v>335</v>
@@ -30487,7 +30639,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C422">
         <v>1022</v>
@@ -30555,7 +30707,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="C423">
         <v>476</v>
@@ -30623,7 +30775,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C424">
         <v>582</v>
@@ -30691,7 +30843,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C425">
         <v>434</v>
@@ -30759,7 +30911,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C426">
         <v>628</v>
@@ -30827,7 +30979,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="C427">
         <v>655</v>
@@ -30895,7 +31047,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C428">
         <v>785</v>
@@ -30963,7 +31115,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C429">
         <v>419</v>
@@ -31031,7 +31183,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="C430">
         <v>819</v>
@@ -31099,7 +31251,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C431">
         <v>677</v>
@@ -31167,7 +31319,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C432">
         <v>896</v>
@@ -31235,7 +31387,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C433">
         <v>599</v>
@@ -31303,7 +31455,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C434">
         <v>1149</v>
@@ -31371,7 +31523,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C435">
         <v>873</v>
@@ -31439,7 +31591,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="C436">
         <v>665</v>
@@ -31507,7 +31659,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C437">
         <v>841</v>
@@ -31575,7 +31727,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C438">
         <v>946</v>
@@ -31643,7 +31795,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C439">
         <v>873</v>
@@ -31711,7 +31863,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C440">
         <v>1024</v>
@@ -31779,7 +31931,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="C441">
         <v>1026</v>
@@ -31847,7 +31999,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C442">
         <v>975</v>
@@ -31915,7 +32067,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="C443">
         <v>727</v>
@@ -31983,7 +32135,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C444">
         <v>803</v>
@@ -32051,7 +32203,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C445">
         <v>621</v>
@@ -32119,7 +32271,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="C446">
         <v>763</v>
@@ -32187,7 +32339,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="C447">
         <v>1202</v>
@@ -32255,7 +32407,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="C448">
         <v>965</v>
@@ -32323,7 +32475,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="C449">
         <v>651</v>
@@ -32391,7 +32543,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="C450">
         <v>709</v>
@@ -32459,7 +32611,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="C451">
         <v>723</v>
@@ -32527,7 +32679,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C452">
         <v>826</v>
@@ -32595,7 +32747,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="C453">
         <v>950</v>
@@ -32663,7 +32815,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="C454">
         <v>844</v>
@@ -32731,7 +32883,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C455">
         <v>933</v>
@@ -32799,7 +32951,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C456">
         <v>1014</v>
@@ -32867,7 +33019,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="C457">
         <v>1067</v>
@@ -32935,7 +33087,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="C458">
         <v>849</v>
@@ -33003,7 +33155,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="C459">
         <v>656</v>
@@ -33071,7 +33223,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="C460">
         <v>878</v>
@@ -33139,7 +33291,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C461">
         <v>816</v>
@@ -33207,7 +33359,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="C462">
         <v>397</v>
@@ -33275,7 +33427,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C463">
         <v>742</v>
@@ -33343,7 +33495,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C464">
         <v>526</v>
@@ -33411,7 +33563,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="C465">
         <v>1090</v>
@@ -33479,7 +33631,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="C466">
         <v>690</v>
@@ -33547,7 +33699,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="C467">
         <v>957</v>
@@ -33615,7 +33767,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="C468">
         <v>927</v>
@@ -33683,7 +33835,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="C469">
         <v>1120</v>
@@ -33751,7 +33903,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C470">
         <v>854</v>
@@ -33819,7 +33971,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C471">
         <v>686</v>
@@ -33887,7 +34039,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="C472">
         <v>826</v>
@@ -33955,7 +34107,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C473">
         <v>900</v>
@@ -34023,7 +34175,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C474">
         <v>749</v>
@@ -34091,7 +34243,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="C475">
         <v>613</v>
@@ -34159,7 +34311,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="C476">
         <v>1148</v>
@@ -34227,7 +34379,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="C477">
         <v>1167</v>
@@ -34295,7 +34447,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="C478">
         <v>1165</v>
@@ -34363,7 +34515,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="C479">
         <v>684</v>
@@ -34431,7 +34583,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="C480">
         <v>1038</v>
@@ -34499,7 +34651,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="C481">
         <v>1116</v>
@@ -34567,7 +34719,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="C482">
         <v>1068</v>
@@ -34635,7 +34787,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C483">
         <v>800</v>
@@ -34703,7 +34855,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="C484">
         <v>1005</v>
@@ -34771,7 +34923,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="C485">
         <v>1176</v>
@@ -34839,7 +34991,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="C486">
         <v>908</v>
@@ -34907,7 +35059,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="C487">
         <v>738</v>
@@ -34975,7 +35127,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="C488">
         <v>1243</v>
@@ -35043,7 +35195,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="C489">
         <v>919</v>
@@ -35111,7 +35263,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="C490">
         <v>825</v>
@@ -35179,7 +35331,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="C491">
         <v>626</v>
@@ -35247,7 +35399,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="C492">
         <v>763</v>
@@ -35315,7 +35467,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="C493">
         <v>778</v>
@@ -35383,7 +35535,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="C494">
         <v>1028</v>
@@ -35451,7 +35603,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C495">
         <v>740</v>
@@ -35519,7 +35671,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="C496">
         <v>1096</v>
@@ -35587,7 +35739,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="C497">
         <v>783</v>
@@ -35655,7 +35807,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="C498">
         <v>927</v>
@@ -35723,7 +35875,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="C499">
         <v>818</v>
@@ -35791,7 +35943,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="C500">
         <v>718</v>
@@ -35859,7 +36011,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="C501">
         <v>668</v>
@@ -35927,7 +36079,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="C502">
         <v>729</v>
@@ -35995,7 +36147,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="C503">
         <v>1167</v>
@@ -36063,7 +36215,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="C504">
         <v>1037</v>
@@ -36131,7 +36283,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="C505">
         <v>592</v>
@@ -36199,7 +36351,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="C506">
         <v>695</v>
@@ -36267,7 +36419,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="C507">
         <v>746</v>
@@ -36335,7 +36487,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="C508">
         <v>730</v>
@@ -36403,7 +36555,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="C509">
         <v>1068</v>
@@ -36471,7 +36623,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="C510">
         <v>675</v>
@@ -36539,7 +36691,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="C511">
         <v>1009</v>
@@ -36607,7 +36759,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="C512">
         <v>1038</v>
@@ -36675,7 +36827,7 @@
         <v>511</v>
       </c>
       <c r="B513" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="C513">
         <v>812</v>
